--- a/data/equipment.xlsx
+++ b/data/equipment.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46198</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46168</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46001</v>
+        <v>46004</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="5">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="6">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="7">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="8">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="9">
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46011</v>
+        <v>46014</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46203</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="11">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="12">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46013</v>
+        <v>46016</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
     </row>
   </sheetData>
